--- a/cloudflare-deploy/public/library/admin/admin-en.xlsx
+++ b/cloudflare-deploy/public/library/admin/admin-en.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2240,6 +2240,60 @@
       <c r="E39" s="20" t="inlineStr">
         <is>
           <t>Fill in nationality and contact details when registering a new teacher — later questions drop sharply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="54" customHeight="1">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>🗂️</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>Teacher Management, redesigned (roster filters · groups · detail tabs)</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>Open Teachers in the admin menu (menus are tidied into four bundles). → Filter to just the teachers you want with the status/group dropdowns above the roster. → Applied filters show as chips; remove a chip to clear it. → Tap a teacher to open the Profile / Payroll / Evaluation detail tabs. → The summary numbers on the payroll/evaluation tabs load only as needed when opened.</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>The more teachers you have, the more the status/group filters help. Keep your usual conditions filtered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="54" customHeight="1">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>🌟</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>Sending the Parent Monthly Report (pentagon)</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>Open the Monthly Report screen. → Enter a student ID and month, press View Report to preview. → Check the pentagon and teacher's note; top up evaluations if needed. → Append ?uid=ID&amp;period=YYYY-MM to the URL and send the KakaoTalk link.</t>
+        </is>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>Sending the report link ahead of a booked consultation makes the meeting much smoother.</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F408"/>
+  <dimension ref="A1:F436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6795,11 +6849,334 @@
       <c r="E408" s="33" t="n"/>
       <c r="F408" s="33" t="n"/>
     </row>
+    <row r="410" ht="26" customHeight="1">
+      <c r="A410" s="21" t="inlineStr">
+        <is>
+          <t>37  🗂️ Teacher Management, redesigned (roster filters · groups · detail tabs)  —  Easy-to-search roster · detail at a glance</t>
+        </is>
+      </c>
+      <c r="B410" s="22" t="n"/>
+      <c r="C410" s="22" t="n"/>
+      <c r="D410" s="22" t="n"/>
+      <c r="E410" s="22" t="n"/>
+      <c r="F410" s="22" t="n"/>
+    </row>
+    <row r="411" ht="42" customHeight="1">
+      <c r="A411" s="23" t="inlineStr">
+        <is>
+          <t>📖 The teacher-management screen is now easier to search and read. Scattered menus are grouped into four bundles in the sidebar, and above the roster there are status/group dropdown filters with applied-filter chips. Tapping a teacher opens a detail view split into Profile / Payroll / Evaluation tabs, with a manager badge and employment status (active / on-leave / left) shown at a glance.</t>
+        </is>
+      </c>
+      <c r="B411" s="24" t="n"/>
+      <c r="C411" s="24" t="n"/>
+      <c r="D411" s="24" t="n"/>
+      <c r="E411" s="24" t="n"/>
+      <c r="F411" s="24" t="n"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B412" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="413" ht="30" customHeight="1">
+      <c r="A413" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B413" s="28" t="inlineStr">
+        <is>
+          <t>Open Teachers in the admin menu (menus are tidied into four bundles).</t>
+        </is>
+      </c>
+    </row>
+    <row r="414" ht="30" customHeight="1">
+      <c r="A414" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B414" s="28" t="inlineStr">
+        <is>
+          <t>Filter to just the teachers you want with the status/group dropdowns above the roster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="415" ht="30" customHeight="1">
+      <c r="A415" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B415" s="28" t="inlineStr">
+        <is>
+          <t>Applied filters show as chips; remove a chip to clear it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="416" ht="30" customHeight="1">
+      <c r="A416" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B416" s="28" t="inlineStr">
+        <is>
+          <t>Tap a teacher to open the Profile / Payroll / Evaluation detail tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="417" ht="30" customHeight="1">
+      <c r="A417" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B417" s="28" t="inlineStr">
+        <is>
+          <t>The summary numbers on the payroll/evaluation tabs load only as needed when opened.</t>
+        </is>
+      </c>
+    </row>
+    <row r="418" ht="24" customHeight="1">
+      <c r="A418" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B418" s="30" t="inlineStr">
+        <is>
+          <t>Managers are marked with a badge, and status shows as active / on-leave / left (3 states).</t>
+        </is>
+      </c>
+      <c r="C418" s="31" t="n"/>
+      <c r="D418" s="31" t="n"/>
+      <c r="E418" s="31" t="n"/>
+      <c r="F418" s="31" t="n"/>
+    </row>
+    <row r="419" ht="24" customHeight="1">
+      <c r="A419" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B419" s="30" t="inlineStr">
+        <is>
+          <t>A blank name falls back to the ID, so there are no empty cells.</t>
+        </is>
+      </c>
+      <c r="C419" s="31" t="n"/>
+      <c r="D419" s="31" t="n"/>
+      <c r="E419" s="31" t="n"/>
+      <c r="F419" s="31" t="n"/>
+    </row>
+    <row r="420" ht="24" customHeight="1">
+      <c r="A420" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B420" s="30" t="inlineStr">
+        <is>
+          <t>Detail tabs reuse existing APIs for speed, and the screen is bilingual (KO/EN).</t>
+        </is>
+      </c>
+      <c r="C420" s="31" t="n"/>
+      <c r="D420" s="31" t="n"/>
+      <c r="E420" s="31" t="n"/>
+      <c r="F420" s="31" t="n"/>
+    </row>
+    <row r="421" ht="24" customHeight="1">
+      <c r="A421" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B421" s="30" t="inlineStr">
+        <is>
+          <t>The duplicate payroll entry was tidied and bug reports moved to a separate system.</t>
+        </is>
+      </c>
+      <c r="C421" s="31" t="n"/>
+      <c r="D421" s="31" t="n"/>
+      <c r="E421" s="31" t="n"/>
+      <c r="F421" s="31" t="n"/>
+    </row>
+    <row r="422" ht="26" customHeight="1">
+      <c r="A422" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · This is a filtering/detail cleanup. Registering, editing and deleting teachers works exactly as before.</t>
+        </is>
+      </c>
+      <c r="B422" s="35" t="n"/>
+      <c r="C422" s="35" t="n"/>
+      <c r="D422" s="35" t="n"/>
+      <c r="E422" s="35" t="n"/>
+      <c r="F422" s="35" t="n"/>
+    </row>
+    <row r="423" ht="30" customHeight="1">
+      <c r="A423" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · The more teachers you have, the more the status/group filters help. Keep your usual conditions filtered.</t>
+        </is>
+      </c>
+      <c r="B423" s="33" t="n"/>
+      <c r="C423" s="33" t="n"/>
+      <c r="D423" s="33" t="n"/>
+      <c r="E423" s="33" t="n"/>
+      <c r="F423" s="33" t="n"/>
+    </row>
+    <row r="425" ht="26" customHeight="1">
+      <c r="A425" s="21" t="inlineStr">
+        <is>
+          <t>38  🌟 Sending the Parent Monthly Report (pentagon)  —  Preview the 5-axis report, then share the link</t>
+        </is>
+      </c>
+      <c r="B425" s="22" t="n"/>
+      <c r="C425" s="22" t="n"/>
+      <c r="D425" s="22" t="n"/>
+      <c r="E425" s="22" t="n"/>
+      <c r="F425" s="22" t="n"/>
+    </row>
+    <row r="426" ht="42" customHeight="1">
+      <c r="A426" s="23" t="inlineStr">
+        <is>
+          <t>📖 The monthly report sent to parents is renewed as a pentagon 5-axis graph — Pronunciation &amp; Fluency / Vocabulary / Sentence Building / Class Attitude / Participation — at a glance, with attendance, judgment and a teacher's note. Admins and teachers enter a student ID and month to preview, then send the KakaoTalk link.</t>
+        </is>
+      </c>
+      <c r="B426" s="24" t="n"/>
+      <c r="C426" s="24" t="n"/>
+      <c r="D426" s="24" t="n"/>
+      <c r="E426" s="24" t="n"/>
+      <c r="F426" s="24" t="n"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B427" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="428" ht="30" customHeight="1">
+      <c r="A428" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B428" s="28" t="inlineStr">
+        <is>
+          <t>Open the Monthly Report screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429" ht="30" customHeight="1">
+      <c r="A429" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B429" s="28" t="inlineStr">
+        <is>
+          <t>Enter a student ID and month, press View Report to preview.</t>
+        </is>
+      </c>
+    </row>
+    <row r="430" ht="30" customHeight="1">
+      <c r="A430" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B430" s="28" t="inlineStr">
+        <is>
+          <t>Check the pentagon and teacher's note; top up evaluations if needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="431" ht="30" customHeight="1">
+      <c r="A431" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B431" s="28" t="inlineStr">
+        <is>
+          <t>Append ?uid=ID&amp;period=YYYY-MM to the URL and send the KakaoTalk link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="432" ht="24" customHeight="1">
+      <c r="A432" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B432" s="30" t="inlineStr">
+        <is>
+          <t>Only axes with real records are filled, so it's trustworthy.</t>
+        </is>
+      </c>
+      <c r="C432" s="31" t="n"/>
+      <c r="D432" s="31" t="n"/>
+      <c r="E432" s="31" t="n"/>
+      <c r="F432" s="31" t="n"/>
+    </row>
+    <row r="433" ht="24" customHeight="1">
+      <c r="A433" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B433" s="30" t="inlineStr">
+        <is>
+          <t>Compiled on a two-month cycle — conveys change without tiring parents.</t>
+        </is>
+      </c>
+      <c r="C433" s="31" t="n"/>
+      <c r="D433" s="31" t="n"/>
+      <c r="E433" s="31" t="n"/>
+      <c r="F433" s="31" t="n"/>
+    </row>
+    <row r="434" ht="24" customHeight="1">
+      <c r="A434" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B434" s="30" t="inlineStr">
+        <is>
+          <t>The Print/PDF button makes a paper report for consultations instantly.</t>
+        </is>
+      </c>
+      <c r="C434" s="31" t="n"/>
+      <c r="D434" s="31" t="n"/>
+      <c r="E434" s="31" t="n"/>
+      <c r="F434" s="31" t="n"/>
+    </row>
+    <row r="435" ht="26" customHeight="1">
+      <c r="A435" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Report access passes an approval gate — admins via their login session, parents only via the issued link (token).</t>
+        </is>
+      </c>
+      <c r="B435" s="35" t="n"/>
+      <c r="C435" s="35" t="n"/>
+      <c r="D435" s="35" t="n"/>
+      <c r="E435" s="35" t="n"/>
+      <c r="F435" s="35" t="n"/>
+    </row>
+    <row r="436" ht="30" customHeight="1">
+      <c r="A436" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Sending the report link ahead of a booked consultation makes the meeting much smoother.</t>
+        </is>
+      </c>
+      <c r="B436" s="33" t="n"/>
+      <c r="C436" s="33" t="n"/>
+      <c r="D436" s="33" t="n"/>
+      <c r="E436" s="33" t="n"/>
+      <c r="F436" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="372">
+  <mergeCells count="398">
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="A394:F394"/>
     <mergeCell ref="B122:F122"/>
+    <mergeCell ref="B432:F432"/>
     <mergeCell ref="B214:F214"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B238:F238"/>
@@ -6814,15 +7191,19 @@
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B133:F133"/>
     <mergeCell ref="B369:F369"/>
+    <mergeCell ref="B418:F418"/>
     <mergeCell ref="B356:F356"/>
     <mergeCell ref="B160:F160"/>
     <mergeCell ref="B368:F368"/>
     <mergeCell ref="B306:F306"/>
+    <mergeCell ref="B433:F433"/>
     <mergeCell ref="B233:F233"/>
     <mergeCell ref="B227:F227"/>
+    <mergeCell ref="B420:F420"/>
     <mergeCell ref="B224:F224"/>
     <mergeCell ref="B72:F72"/>
     <mergeCell ref="A267:F267"/>
+    <mergeCell ref="A425:F425"/>
     <mergeCell ref="B228:F228"/>
     <mergeCell ref="B293:F293"/>
     <mergeCell ref="A135:F135"/>
@@ -6830,6 +7211,7 @@
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B88:F88"/>
     <mergeCell ref="A199:F199"/>
+    <mergeCell ref="A435:F435"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B317:F317"/>
     <mergeCell ref="B388:F388"/>
@@ -6919,6 +7301,7 @@
     <mergeCell ref="B105:F105"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B341:F341"/>
+    <mergeCell ref="B412:F412"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="A254:F254"/>
     <mergeCell ref="A311:F311"/>
@@ -6955,12 +7338,15 @@
     <mergeCell ref="B226:F226"/>
     <mergeCell ref="A245:F245"/>
     <mergeCell ref="B364:F364"/>
+    <mergeCell ref="B413:F413"/>
     <mergeCell ref="A166:F166"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B428:F428"/>
     <mergeCell ref="B284:F284"/>
     <mergeCell ref="A103:F103"/>
     <mergeCell ref="B222:F222"/>
+    <mergeCell ref="B415:F415"/>
     <mergeCell ref="A168:F168"/>
     <mergeCell ref="B63:F63"/>
     <mergeCell ref="B123:F123"/>
@@ -6970,6 +7356,7 @@
     <mergeCell ref="B286:F286"/>
     <mergeCell ref="A128:F128"/>
     <mergeCell ref="A255:F255"/>
+    <mergeCell ref="A426:F426"/>
     <mergeCell ref="A57:F57"/>
     <mergeCell ref="A113:F113"/>
     <mergeCell ref="B248:F248"/>
@@ -6988,8 +7375,10 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="A408:F408"/>
     <mergeCell ref="A187:F187"/>
+    <mergeCell ref="A423:F423"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B129:F129"/>
+    <mergeCell ref="A410:F410"/>
     <mergeCell ref="B194:F194"/>
     <mergeCell ref="B365:F365"/>
     <mergeCell ref="B292:F292"/>
@@ -6997,18 +7386,22 @@
     <mergeCell ref="B131:F131"/>
     <mergeCell ref="B236:F236"/>
     <mergeCell ref="B307:F307"/>
+    <mergeCell ref="B429:F429"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="B223:F223"/>
     <mergeCell ref="B294:F294"/>
     <mergeCell ref="B350:F350"/>
     <mergeCell ref="B195:F195"/>
+    <mergeCell ref="B431:F431"/>
     <mergeCell ref="A200:F200"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="A265:F265"/>
+    <mergeCell ref="A436:F436"/>
     <mergeCell ref="A357:F357"/>
     <mergeCell ref="A258:F258"/>
     <mergeCell ref="A329:F329"/>
     <mergeCell ref="A60:F60"/>
+    <mergeCell ref="B434:F434"/>
     <mergeCell ref="A358:F358"/>
     <mergeCell ref="B142:F142"/>
     <mergeCell ref="B313:F313"/>
@@ -7016,12 +7409,14 @@
     <mergeCell ref="B378:F378"/>
     <mergeCell ref="B305:F305"/>
     <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A422:F422"/>
     <mergeCell ref="A360:F360"/>
     <mergeCell ref="B144:F144"/>
     <mergeCell ref="A149:F149"/>
     <mergeCell ref="A385:F385"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B318:F318"/>
+    <mergeCell ref="A411:F411"/>
     <mergeCell ref="A190:F190"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B308:F308"/>
@@ -7108,6 +7503,7 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="A278:F278"/>
     <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B421:F421"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B175:F175"/>
     <mergeCell ref="B162:F162"/>
@@ -7116,10 +7512,12 @@
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="B251:F251"/>
     <mergeCell ref="B216:F216"/>
+    <mergeCell ref="B414:F414"/>
     <mergeCell ref="A398:F398"/>
     <mergeCell ref="B109:F109"/>
     <mergeCell ref="B280:F280"/>
     <mergeCell ref="B351:F351"/>
+    <mergeCell ref="B416:F416"/>
     <mergeCell ref="B193:F193"/>
     <mergeCell ref="B295:F295"/>
     <mergeCell ref="B282:F282"/>
@@ -7155,13 +7553,17 @@
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B430:F430"/>
     <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B417:F417"/>
     <mergeCell ref="B196:F196"/>
     <mergeCell ref="B367:F367"/>
+    <mergeCell ref="B427:F427"/>
     <mergeCell ref="B112:F112"/>
     <mergeCell ref="B283:F283"/>
     <mergeCell ref="B354:F354"/>
     <mergeCell ref="B348:F348"/>
+    <mergeCell ref="B419:F419"/>
     <mergeCell ref="B298:F298"/>
     <mergeCell ref="B285:F285"/>
     <mergeCell ref="B64:F64"/>

--- a/cloudflare-deploy/public/library/admin/admin-en.xlsx
+++ b/cloudflare-deploy/public/library/admin/admin-en.xlsx
@@ -1111,6 +1111,156 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1241</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="2962275"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1260</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="4724400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1288</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="3895725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1312</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="2181225"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1327</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="3800475"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1350</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8572500" cy="1200150"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1413,7 +1563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2796,6 +2946,213 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>A.i content payment (agencies)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>10-1</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Agency login · open the menu</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>• An agency logs in at mangoi.ai/admin/login with its agency ID and gets the agency screen.
+• ④ Left menu Settlement &amp; stats › 🤖 A.i content payment. This menu appears only for agency accounts (not for HQ or branch accounts).
+• HQ uses Finance › 🏢 AI Usage Fee (A.i Learning Fee Management) to see each academy’s headcount and estimated invoice, set custom rates, and turn auto-billing on or off. There is no pay button there.</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Screens!10-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>A.i content payment (agencies)</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>10-2</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Load the student list</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>• Check the due date at the top (last day of this month · D-days left). The payment is for next month.
+• Counters: Signed up for A.i (to be paid) · Not signed up · Video class (included) — video-class students get A.i with their tuition and are not paid here.
+• ⑤ Load my students and choose only loads the list. Nothing is paid at this point.
+• If HQ has not turned on auto-billing yet, the agency only sees «Head office has not opened A.i content payment yet (test period)» — it is not broken.</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Screens!10-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>A.i content payment (agencies)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>10-3</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Choose next month’s students</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>• ⑥ Only students checked under Paying for A.i content are paid. Unchecking a student who left removes them before payment.
+• Search by name or ID; Unselect all shown / Select all shown changes many at once (it asks how many first).
+• The server recalculates the amount every time a check changes.</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Screens!10-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>A.i content payment (agencies)</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>10-4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Not signed up · video-class students</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>• ⑦ Checking a student under Not signed up adds them to the payment.
+• 📹 Video-class students are folded away. A.i is included in their tuition, so they are not chosen — check one only if the classification is wrong.
+• Students the academy changed get a «✔ confirmed by academy» tag, and automatic classification no longer changes them.</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Screens!10-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>A.i content payment (agencies)</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>10-5</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Check the amount · pay by card</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>• ⑧ Check the number of students and the total, then ⑨ Pay OOO KRW → confirm → pay in the Toss card window.
+• Price per student per month: 20 or fewer 7,500 · 21–50 6,500 · 51–70 5,500 · 71 or more 4,500 KRW. No minimum charge (since 2026-10-26).
+• The total never goes down as students are added (e.g. 21–23 students = 150,000 KRW). The server recalculates the amount at the moment of payment — the screen number is for display. Academies with an HQ custom rate pay that rate × students.
+• The demo account (testagency) does not open the payment window (sample data).</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Screens!10-5</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>A.i content payment (agencies)</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>10-6</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Check the payment · extra payment</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>• ⑩ A ✅ under Past payments means paid. After paying, «Paid» appears and paid students are pinned at the top.
+• To add students in the same month, check them below and press Pay extra — only the added students are charged.
+• Students already paid for cannot be removed or changed on the screen. HQ handles refunds.
+• If an earlier month is unpaid, a «⚠️ Unpaid A.i content invoice(s)» button appears at the top.</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Screens!10-6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2807,7 +3164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1209"/>
+  <dimension ref="A1:A1350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -3083,6 +3440,48 @@
       <c r="A1209" s="3" t="inlineStr">
         <is>
           <t>9-2  Daily handover</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="3" t="inlineStr">
+        <is>
+          <t>10-1  Agency login · open the menu</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="3" t="inlineStr">
+        <is>
+          <t>10-2  Load the student list</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="3" t="inlineStr">
+        <is>
+          <t>10-3  Choose next month’s students</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="3" t="inlineStr">
+        <is>
+          <t>10-4  Not signed up · video-class students</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="3" t="inlineStr">
+        <is>
+          <t>10-5  Check the amount · pay by card</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="3" t="inlineStr">
+        <is>
+          <t>10-6  Check the payment · extra payment</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -3213,6 +3612,42 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>An agency says it has no «A.i content payment» menu</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Check that they logged in with the agency ID. The menu appears only for agency accounts (not branch or HQ).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>An agency sees «Head office has not opened A.i content payment yet»</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>It is not broken. It shows until HQ presses «Turn ON» for auto-billing in Finance › 🏢 AI Usage Fee (test period).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>An agency wants to remove a student they already paid for</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>It cannot be done on the agency screen. HQ handles refunds.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
